--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/ene-2026.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/ene-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC ene-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC ene-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5799,7 +5799,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">

--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/ene-2026.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/ene-2026.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo del CCP Talca</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1215,12 +1215,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DEL TERRITORIO MARITIMO Y M.M.</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Chillan Viejo</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>DIRECCION DE SANIDAD DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES</t>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>CORP DE EDUCACION Y SALUD DE LAS CONDES</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN CO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE ANDALIÉN COSTA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOLTEN</t>
+          <t>Ilustre Municipalidad de Tolten</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>PRODUCTOS Y SERVICIOS INFORMATICOS TORRES SPA</t>
+          <t>PRODUCTOS Y SERVICIOS INFORMATICOS TORRES SpA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Tic Services SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -6272,7 +6272,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -6465,7 +6465,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Direccion Admin. Salud Municipal Florida</t>
+          <t>I MUNICIPALIDAD DE FLORIDA</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>INSTITUTO GEOGRAFICO MILITAR</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Departamento de Salud Municipal</t>
+          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Educación Municipal</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PICHILEMU</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Valparaíso para el Desarrollo Social</t>
+          <t>CORP MUNICIPAL DE VALPARAISO PARA EL DESARROLLO SOCIAL</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Fondos Extrapresupuestarios Escipol</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8722,7 +8722,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>DIRECCION DE BIENESTAR SOCIAL DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>DIRECCION DE BIENESTAR SOCIAL DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Santa Rosa</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA ROSA</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9210,7 +9210,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>DIRECCION DE EDUCACION</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9454,7 +9454,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9505,7 +9505,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">I. Municipalidad de O'Higgins </t>
+          <t>I MUNICIPALIDAD DE O HIGGINS</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">

--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/ene-2026.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/ene-2026.xlsx
@@ -562,7 +562,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1009,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1074,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1261,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1326,11 @@
           <t>77.137.827-7</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1391,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1456,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1521,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1586,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1651,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1725,7 +1781,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1786,7 +1846,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1847,7 +1911,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1908,7 +1976,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1969,7 +2041,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2091,7 +2167,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2152,7 +2232,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2274,7 +2358,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2396,7 +2484,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2457,7 +2549,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2518,7 +2614,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2579,7 +2679,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2640,7 +2744,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2701,7 +2809,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2762,7 +2874,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3006,7 +3122,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3067,7 +3187,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3128,7 +3252,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3250,7 +3378,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3494,7 +3626,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3616,7 +3752,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3677,7 +3817,11 @@
           <t>76.819.088-7</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3982,7 +4126,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4043,7 +4191,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4165,7 +4317,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4287,7 +4443,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4409,7 +4569,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4531,7 +4695,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4592,7 +4760,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4653,7 +4825,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4714,7 +4890,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4836,7 +5016,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4958,7 +5142,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5019,7 +5207,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5202,7 +5394,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5263,7 +5459,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5385,7 +5585,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5446,7 +5650,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5507,7 +5715,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5568,7 +5780,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5629,7 +5845,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5690,7 +5910,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5873,7 +6097,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5995,7 +6223,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6056,7 +6288,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6117,7 +6353,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6178,7 +6418,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6239,7 +6483,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6300,7 +6548,11 @@
           <t>76.819.088-7</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6422,7 +6674,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6483,7 +6739,11 @@
           <t>76.819.088-7</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6544,7 +6804,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6666,7 +6930,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6727,7 +6995,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6788,7 +7060,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6849,7 +7125,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6910,7 +7190,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6971,7 +7255,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7093,7 +7381,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7337,7 +7629,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7520,7 +7816,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7581,7 +7881,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7642,7 +7946,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7703,7 +8011,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7825,7 +8137,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7886,7 +8202,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8008,7 +8328,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8069,7 +8393,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8191,7 +8519,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8313,7 +8645,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8374,7 +8710,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8435,7 +8775,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8496,7 +8840,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8557,7 +8905,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8618,7 +8970,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8740,7 +9096,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8923,7 +9283,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8984,7 +9348,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9045,7 +9413,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9167,7 +9539,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9228,7 +9604,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9289,7 +9669,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9411,7 +9795,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9472,7 +9860,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9533,7 +9925,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9594,7 +9990,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9655,7 +10055,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9716,7 +10120,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9777,7 +10185,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9838,7 +10250,11 @@
           <t>78.218.816-K</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9899,7 +10315,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9960,7 +10380,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/ene-2026.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/ene-2026.xlsx
@@ -5114,7 +5114,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
